--- a/docs/sample-output/07-self-storage/proforma.xlsx
+++ b/docs/sample-output/07-self-storage/proforma.xlsx
@@ -264,7 +264,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 5 at 6.74% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 5 at 7.05% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Bayside Climate Storage · 5-Year Before-Tax</t>
@@ -1055,7 +1055,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>17790423.49</v>
+        <v>17701928.51</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1063,7 +1063,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>0.05846134020275647</v>
+        <v>0.058753598480101414</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1071,7 +1071,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6">
-        <v>6342285.974184997</v>
+        <v>6310737.513814999</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1087,7 +1087,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>0.06739052480378427</v>
+        <v>0.07048130235002881</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1095,7 +1095,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>1.370334919203858</v>
+        <v>1.3891327759275178</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1111,7 +1111,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="7">
-        <v>0.06739052480378427</v>
+        <v>0.07048130235002881</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1126,7 +1126,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="6">
-        <v>17790423.49</v>
+        <v>17701928.51</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1142,7 +1142,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="6">
-        <v>115637.752685</v>
+        <v>115062.53531500003</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1150,7 +1150,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="6">
-        <v>17790423.49</v>
+        <v>17701928.51</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1158,7 +1158,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="6">
-        <v>-11563775.2685</v>
+        <v>-11506253.531500002</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1166,7 +1166,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="10">
-        <v>6342285.974184997</v>
+        <v>6310737.513814999</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1174,7 +1174,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>10.367379656177155</v>
+        <v>10.315809155011657</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1182,7 +1182,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>152.00293480861242</v>
+        <v>151.2468259569378</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1197,7 +1197,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="6">
-        <v>11563775.2685</v>
+        <v>11506253.531500002</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1229,7 +1229,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="12">
-        <v>78079.43873505948</v>
+        <v>77691.04784750394</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1237,7 +1237,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="6">
-        <v>936953.2648207138</v>
+        <v>932292.5741700473</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1472,19 +1472,19 @@
         <v>60</v>
       </c>
       <c r="B13" s="16">
-        <v>-936953.2648207138</v>
+        <v>-932292.5741700473</v>
       </c>
       <c r="C13" s="16">
-        <v>-936953.2648207138</v>
+        <v>-932292.5741700473</v>
       </c>
       <c r="D13" s="16">
-        <v>-936953.2648207138</v>
+        <v>-932292.5741700473</v>
       </c>
       <c r="E13" s="16">
-        <v>-936953.2648207138</v>
+        <v>-932292.5741700473</v>
       </c>
       <c r="F13" s="16">
-        <v>-936953.2648207138</v>
+        <v>-932292.5741700473</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1492,19 +1492,19 @@
         <v>61</v>
       </c>
       <c r="B14" s="18">
-        <v>103098.73517928622</v>
+        <v>107759.4258299527</v>
       </c>
       <c r="C14" s="18">
-        <v>134300.29517928627</v>
+        <v>138960.98582995276</v>
       </c>
       <c r="D14" s="18">
-        <v>166437.90197928622</v>
+        <v>171098.5926299527</v>
       </c>
       <c r="E14" s="18">
-        <v>199539.63698328636</v>
+        <v>204200.32763395284</v>
       </c>
       <c r="F14" s="18">
-        <v>233634.42403740645</v>
+        <v>238295.11468807294</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1648,19 +1648,19 @@
         <v>68</v>
       </c>
       <c r="B9" s="16">
-        <v>-11372845.862297691</v>
+        <v>-11316273.866263261</v>
       </c>
       <c r="C9" s="16">
-        <v>-11169129.560160264</v>
+        <v>-11113570.911002792</v>
       </c>
       <c r="D9" s="16">
-        <v>-10951769.999985585</v>
+        <v>-10897292.56342214</v>
       </c>
       <c r="E9" s="16">
-        <v>-10719853.467515552</v>
+        <v>-10666529.654355966</v>
       </c>
       <c r="F9" s="16">
-        <v>-10472405.055355992</v>
+        <v>-10420312.125896132</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1668,19 +1668,19 @@
         <v>69</v>
       </c>
       <c r="B10" s="18">
-        <v>4910154.137702309</v>
+        <v>4966726.133736739</v>
       </c>
       <c r="C10" s="18">
-        <v>5602170.439839736</v>
+        <v>5657729.088997208</v>
       </c>
       <c r="D10" s="18">
-        <v>6323030.000014415</v>
+        <v>6377507.43657786</v>
       </c>
       <c r="E10" s="18">
-        <v>7072696.532484448</v>
+        <v>7126020.345644034</v>
       </c>
       <c r="F10" s="18">
-        <v>7854044.944644008</v>
+        <v>7906137.874103868</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1718,19 +1718,19 @@
         <v>71</v>
       </c>
       <c r="B13" s="21">
-        <v>0.6635265964000987</v>
+        <v>0.6602260132008904</v>
       </c>
       <c r="C13" s="21">
-        <v>0.6326684921355084</v>
+        <v>0.6295214065369203</v>
       </c>
       <c r="D13" s="21">
-        <v>0.6022750769899684</v>
+        <v>0.5992791774869193</v>
       </c>
       <c r="E13" s="21">
-        <v>0.5723665688245797</v>
+        <v>0.5695194433421947</v>
       </c>
       <c r="F13" s="21">
-        <v>0.542864810292675</v>
+        <v>0.5401644355345048</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1738,19 +1738,19 @@
         <v>72</v>
       </c>
       <c r="B14" s="22">
-        <v>1.1100361555376128</v>
+        <v>1.1155854168696808</v>
       </c>
       <c r="C14" s="22">
-        <v>1.1433372402037414</v>
+        <v>1.1490529793757713</v>
       </c>
       <c r="D14" s="22">
-        <v>1.1776373574098535</v>
+        <v>1.1835245687570444</v>
       </c>
       <c r="E14" s="22">
-        <v>1.2129664781321492</v>
+        <v>1.2190303058197558</v>
       </c>
       <c r="F14" s="22">
-        <v>1.2493554724761138</v>
+        <v>1.2556012149943485</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1758,19 +1758,19 @@
         <v>73</v>
       </c>
       <c r="B15" s="21">
-        <v>0.0899405233888561</v>
+        <v>0.09039015150784832</v>
       </c>
       <c r="C15" s="21">
-        <v>0.09263873909052178</v>
+        <v>0.09310185605308377</v>
       </c>
       <c r="D15" s="21">
-        <v>0.09541790126323743</v>
+        <v>0.09589491173467628</v>
       </c>
       <c r="E15" s="21">
-        <v>0.09828043830113457</v>
+        <v>0.09877175908671658</v>
       </c>
       <c r="F15" s="21">
-        <v>0.10122885145016862</v>
+        <v>0.10173491185931809</v>
       </c>
     </row>
   </sheetData>
@@ -1846,19 +1846,19 @@
         <v>75</v>
       </c>
       <c r="B5" s="21">
-        <v>0.016255768913437354</v>
+        <v>0.017075567727869168</v>
       </c>
       <c r="C5" s="21">
-        <v>0.021175376784637066</v>
+        <v>0.022019769563501837</v>
       </c>
       <c r="D5" s="21">
-        <v>0.026242572891972755</v>
+        <v>0.027112297454203467</v>
       </c>
       <c r="E5" s="21">
-        <v>0.03146178488252854</v>
+        <v>0.03235760118162617</v>
       </c>
       <c r="F5" s="21">
-        <v>0.036837573232801</v>
+        <v>0.037760264020871556</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1866,19 +1866,19 @@
         <v>76</v>
       </c>
       <c r="B6" s="21">
-        <v>0.020997046587122203</v>
+        <v>0.021696268916055455</v>
       </c>
       <c r="C6" s="21">
-        <v>0.02397290418445896</v>
+        <v>0.024561265420112683</v>
       </c>
       <c r="D6" s="21">
-        <v>0.026322491270626074</v>
+        <v>0.026828442668467258</v>
       </c>
       <c r="E6" s="21">
-        <v>0.028212667695667902</v>
+        <v>0.02865559144225228</v>
       </c>
       <c r="F6" s="21">
-        <v>0.029747018979911905</v>
+        <v>0.03014052100818983</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1886,19 +1886,19 @@
         <v>77</v>
       </c>
       <c r="B7" s="23">
-        <v>0.7904488844065113</v>
+        <v>0.8041034108070576</v>
       </c>
       <c r="C7" s="23">
-        <v>0.9207357558405761</v>
+        <v>0.9356195670841213</v>
       </c>
       <c r="D7" s="23">
-        <v>1.060637593406011</v>
+        <v>1.0767880023518477</v>
       </c>
       <c r="E7" s="23">
-        <v>1.2103006917457693</v>
+        <v>1.2277550223894451</v>
       </c>
       <c r="F7" s="23">
-        <v>1.370334919203858</v>
+        <v>1.3891327759275178</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1906,19 +1906,19 @@
         <v>78</v>
       </c>
       <c r="B8" s="21">
-        <v>-0.026270959219258927</v>
+        <v>-0.021403120557610983</v>
       </c>
       <c r="C8" s="21">
-        <v>0.031121215108853743</v>
+        <v>0.033770670620186814</v>
       </c>
       <c r="D8" s="21">
-        <v>0.050988944639514255</v>
+        <v>0.05283988643501972</v>
       </c>
       <c r="E8" s="21">
-        <v>0.06103874976145855</v>
+        <v>0.06247933908474601</v>
       </c>
       <c r="F8" s="21">
-        <v>0.06710782708907245</v>
+        <v>0.06829891781152406</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1946,19 +1946,19 @@
         <v>80</v>
       </c>
       <c r="B10" s="24">
-        <v>-0.2095511155936104</v>
+        <v>-0.19589658919302894</v>
       </c>
       <c r="C10" s="24">
-        <v>-0.04079585706940028</v>
+        <v>-0.03301717696584482</v>
       </c>
       <c r="D10" s="24">
-        <v>0.020166212164345748</v>
+        <v>0.02542385660902351</v>
       </c>
       <c r="E10" s="24">
-        <v>0.05018622522063497</v>
+        <v>0.054097803429914756</v>
       </c>
       <c r="F10" s="24">
-        <v>0.06739052480378427</v>
+        <v>0.07048130235002881</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1966,19 +1966,19 @@
         <v>81</v>
       </c>
       <c r="B11" s="21">
-        <v>-0.18330000000000002</v>
+        <v>-0.1745</v>
       </c>
       <c r="C11" s="21">
-        <v>-0.0719</v>
+        <v>-0.0668</v>
       </c>
       <c r="D11" s="21">
-        <v>-0.030799999999999998</v>
+        <v>-0.0274</v>
       </c>
       <c r="E11" s="21">
-        <v>-0.010799999999999997</v>
+        <v>-0.008399999999999998</v>
       </c>
       <c r="F11" s="21">
-        <v>0.0002999999999999947</v>
+        <v>0.0021999999999999936</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2072,19 +2072,19 @@
         <v>18</v>
       </c>
       <c r="B6" s="18">
-        <v>16011381</v>
+        <v>15931736</v>
       </c>
       <c r="C6" s="18">
-        <v>16900902</v>
+        <v>16816832</v>
       </c>
       <c r="D6" s="18">
-        <v>17790423</v>
+        <v>17701929</v>
       </c>
       <c r="E6" s="18">
-        <v>18679945</v>
+        <v>18587025</v>
       </c>
       <c r="F6" s="18">
-        <v>19569466</v>
+        <v>19472121</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2092,19 +2092,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="21">
-        <v>0.06495704524175647</v>
+        <v>0.06528177469172224</v>
       </c>
       <c r="C7" s="21">
-        <v>0.06153825399378093</v>
+        <v>0.06184589344770763</v>
       </c>
       <c r="D7" s="21">
-        <v>0.05846134181295183</v>
+        <v>0.05875359685376662</v>
       </c>
       <c r="E7" s="21">
-        <v>0.05567746585977636</v>
+        <v>0.05595580788211131</v>
       </c>
       <c r="F7" s="21">
-        <v>0.053146672474353666</v>
+        <v>0.05341236324486685</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2112,19 +2112,19 @@
         <v>90</v>
       </c>
       <c r="B8" s="16">
-        <v>10407397.65</v>
+        <v>10355628.4</v>
       </c>
       <c r="C8" s="16">
-        <v>10985586.3</v>
+        <v>10930940.8</v>
       </c>
       <c r="D8" s="16">
-        <v>11563774.950000001</v>
+        <v>11506253.85</v>
       </c>
       <c r="E8" s="16">
-        <v>12141964.25</v>
+        <v>12081566.25</v>
       </c>
       <c r="F8" s="16">
-        <v>12720152.9</v>
+        <v>12656878.65</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2132,19 +2132,19 @@
         <v>20</v>
       </c>
       <c r="B9" s="16">
-        <v>5708057.3265</v>
+        <v>5679663.884</v>
       </c>
       <c r="C9" s="16">
-        <v>6025171.563000001</v>
+        <v>5995200.607999999</v>
       </c>
       <c r="D9" s="16">
-        <v>6342285.799499998</v>
+        <v>6310737.6885</v>
       </c>
       <c r="E9" s="16">
-        <v>6659400.392499998</v>
+        <v>6626274.4125000015</v>
       </c>
       <c r="F9" s="16">
-        <v>6976514.628999999</v>
+        <v>6941811.136499999</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2152,19 +2152,19 @@
         <v>91</v>
       </c>
       <c r="B10" s="21">
-        <v>0.06495704524175647</v>
+        <v>0.06528177469172224</v>
       </c>
       <c r="C10" s="21">
-        <v>0.06153825399378093</v>
+        <v>0.06184589344770763</v>
       </c>
       <c r="D10" s="21">
-        <v>0.05846134181295183</v>
+        <v>0.05875359685376662</v>
       </c>
       <c r="E10" s="21">
-        <v>0.05567746585977636</v>
+        <v>0.05595580788211131</v>
       </c>
       <c r="F10" s="21">
-        <v>0.053146672474353666</v>
+        <v>0.05341236324486685</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2172,19 +2172,19 @@
         <v>92</v>
       </c>
       <c r="B11" s="21">
-        <v>0.06690575659900917</v>
+        <v>0.0672402279324739</v>
       </c>
       <c r="C11" s="21">
-        <v>0.06338440161359435</v>
+        <v>0.06370127025113886</v>
       </c>
       <c r="D11" s="21">
-        <v>0.06021518206734039</v>
+        <v>0.06051620475937962</v>
       </c>
       <c r="E11" s="21">
-        <v>0.057347789835569644</v>
+        <v>0.05763448211857465</v>
       </c>
       <c r="F11" s="21">
-        <v>0.054741072648584285</v>
+        <v>0.05501473414221286</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2192,19 +2192,19 @@
         <v>93</v>
       </c>
       <c r="B12" s="21">
-        <v>0.06891292929697944</v>
+        <v>0.06925743477044811</v>
       </c>
       <c r="C12" s="21">
-        <v>0.06528593366200218</v>
+        <v>0.06561230835867303</v>
       </c>
       <c r="D12" s="21">
-        <v>0.0620216375293606</v>
+        <v>0.062331690902161</v>
       </c>
       <c r="E12" s="21">
-        <v>0.05906822353063673</v>
+        <v>0.05936351658213189</v>
       </c>
       <c r="F12" s="21">
-        <v>0.05638330482804181</v>
+        <v>0.056665176166479245</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2212,19 +2212,19 @@
         <v>94</v>
       </c>
       <c r="B13" s="21">
-        <v>0.07098031717588883</v>
+        <v>0.07133515781356158</v>
       </c>
       <c r="C13" s="21">
-        <v>0.06724451167186225</v>
+        <v>0.06758067760943322</v>
       </c>
       <c r="D13" s="21">
-        <v>0.06388228665524143</v>
+        <v>0.06420164162922584</v>
       </c>
       <c r="E13" s="21">
-        <v>0.060840270236555846</v>
+        <v>0.061144422079595855</v>
       </c>
       <c r="F13" s="21">
-        <v>0.05807480397288307</v>
+        <v>0.05836513145147363</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2232,19 +2232,19 @@
         <v>95</v>
       </c>
       <c r="B14" s="21">
-        <v>0.0731097266911655</v>
+        <v>0.07347521254796842</v>
       </c>
       <c r="C14" s="21">
-        <v>0.06926184702201812</v>
+        <v>0.06960809793771623</v>
       </c>
       <c r="D14" s="21">
-        <v>0.06579875525489867</v>
+        <v>0.06612769087810262</v>
       </c>
       <c r="E14" s="21">
-        <v>0.06266547834365252</v>
+        <v>0.06297875474198374</v>
       </c>
       <c r="F14" s="21">
-        <v>0.059817048092069565</v>
+        <v>0.060116085395017844</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2252,19 +2252,19 @@
         <v>96</v>
       </c>
       <c r="B15" s="21">
-        <v>0.034476540411333585</v>
+        <v>0.03538742245892334</v>
       </c>
       <c r="C15" s="21">
-        <v>0.024886663137909857</v>
+        <v>0.02574960690769025</v>
       </c>
       <c r="D15" s="21">
-        <v>0.016255773430114397</v>
+        <v>0.01707556316592026</v>
       </c>
       <c r="E15" s="21">
-        <v>0.008446864725554861</v>
+        <v>0.009227627761557533</v>
       </c>
       <c r="F15" s="21">
-        <v>0.0013478650469498476</v>
+        <v>0.0020931407005632765</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2272,19 +2272,19 @@
         <v>97</v>
       </c>
       <c r="B16" s="21">
-        <v>0.039942771427470186</v>
+        <v>0.04088097993648763</v>
       </c>
       <c r="C16" s="21">
-        <v>0.030065197835843743</v>
+        <v>0.03095402991871755</v>
       </c>
       <c r="D16" s="21">
-        <v>0.02117538143681442</v>
+        <v>0.022019764864694456</v>
       </c>
       <c r="E16" s="21">
-        <v>0.013132205471118099</v>
+        <v>0.013936391398200848</v>
       </c>
       <c r="F16" s="21">
-        <v>0.005820235802154934</v>
+        <v>0.006587869725376765</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2292,19 +2292,19 @@
         <v>98</v>
       </c>
       <c r="B17" s="21">
-        <v>0.045572989374090864</v>
+        <v>0.04653934413837883</v>
       </c>
       <c r="C17" s="21">
-        <v>0.03539908857471563</v>
+        <v>0.036314585620075654</v>
       </c>
       <c r="D17" s="21">
-        <v>0.026242577683715428</v>
+        <v>0.027112292614431863</v>
       </c>
       <c r="E17" s="21">
-        <v>0.017958106439048216</v>
+        <v>0.018786417943943447</v>
       </c>
       <c r="F17" s="21">
-        <v>0.010426777680016158</v>
+        <v>0.011217440620934643</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2312,19 +2312,19 @@
         <v>99</v>
       </c>
       <c r="B18" s="21">
-        <v>0.0513721138591102</v>
+        <v>0.052367459266326806</v>
       </c>
       <c r="C18" s="21">
-        <v>0.0408929960357537</v>
+        <v>0.041835957992474526</v>
       </c>
       <c r="D18" s="21">
-        <v>0.0314617898180235</v>
+        <v>0.03235759619666142</v>
       </c>
       <c r="E18" s="21">
-        <v>0.022928784436016265</v>
+        <v>0.023781945286058353</v>
       </c>
       <c r="F18" s="21">
-        <v>0.015171515814213244</v>
+        <v>0.015985898643359284</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2332,19 +2332,19 @@
         <v>100</v>
       </c>
       <c r="B19" s="21">
-        <v>0.0573452120786801</v>
+        <v>0.05837041784811321</v>
       </c>
       <c r="C19" s="21">
-        <v>0.04655172072062291</v>
+        <v>0.04752297153604536</v>
       </c>
       <c r="D19" s="21">
-        <v>0.0368375783163608</v>
+        <v>0.03776025888635786</v>
       </c>
       <c r="E19" s="21">
-        <v>0.028048582772893352</v>
+        <v>0.028927338448436698</v>
       </c>
       <c r="F19" s="21">
-        <v>0.020058596092436237</v>
+        <v>0.020897410406456658</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2352,19 +2352,19 @@
         <v>101</v>
       </c>
       <c r="B20" s="21">
-        <v>0.08192116595083326</v>
+        <v>0.08732984277436222</v>
       </c>
       <c r="C20" s="21">
-        <v>0.024977956797661436</v>
+        <v>0.030101983536437314</v>
       </c>
       <c r="D20" s="21">
-        <v>-0.026270932399896158</v>
+        <v>-0.02140314764581254</v>
       </c>
       <c r="E20" s="21">
-        <v>-0.07263902543623407</v>
+        <v>-0.0680029751939071</v>
       </c>
       <c r="F20" s="21">
-        <v>-0.11479178839091311</v>
+        <v>-0.1103664567408682</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2372,19 +2372,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21">
-        <v>0.08861383061973833</v>
+        <v>0.09141529188246225</v>
       </c>
       <c r="C21" s="21">
-        <v>0.0587101723267935</v>
+        <v>0.061432516535171455</v>
       </c>
       <c r="D21" s="21">
-        <v>0.031121229723389324</v>
+        <v>0.03377065589352805</v>
       </c>
       <c r="E21" s="21">
-        <v>0.00556396402283243</v>
+        <v>0.008145989768482098</v>
       </c>
       <c r="F21" s="21">
-        <v>-0.01819847576119712</v>
+        <v>-0.015679066948744373</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2392,19 +2392,19 @@
         <v>103</v>
       </c>
       <c r="B22" s="21">
-        <v>0.09086174942057607</v>
+        <v>0.09278941385985204</v>
       </c>
       <c r="C22" s="21">
-        <v>0.07019824150713028</v>
+        <v>0.07208606691643003</v>
       </c>
       <c r="D22" s="21">
-        <v>0.050988954853207716</v>
+        <v>0.05283987615063179</v>
       </c>
       <c r="E22" s="21">
-        <v>0.03306478792491074</v>
+        <v>0.03488144522674359</v>
       </c>
       <c r="F22" s="21">
-        <v>0.016283365393547182</v>
+        <v>0.01806803675089595</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2412,19 +2412,19 @@
         <v>104</v>
       </c>
       <c r="B23" s="21">
-        <v>0.09197367081847671</v>
+        <v>0.09346414162357256</v>
       </c>
       <c r="C23" s="21">
-        <v>0.07596750780723208</v>
+        <v>0.07743207673764363</v>
       </c>
       <c r="D23" s="21">
-        <v>0.0610387577115042</v>
+        <v>0.06247933108161817</v>
       </c>
       <c r="E23" s="21">
-        <v>0.047064602790189244</v>
+        <v>0.048482900359495776</v>
       </c>
       <c r="F23" s="21">
-        <v>0.033941429028712895</v>
+        <v>0.035338925208675945</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2432,19 +2432,19 @@
         <v>105</v>
       </c>
       <c r="B24" s="21">
-        <v>0.09264625405588878</v>
+        <v>0.09387472329156386</v>
       </c>
       <c r="C24" s="21">
-        <v>0.07944234352332463</v>
+        <v>0.08065138502129249</v>
       </c>
       <c r="D24" s="21">
-        <v>0.06710783366271109</v>
+        <v>0.06829891119520262</v>
       </c>
       <c r="E24" s="21">
-        <v>0.05554432217846138</v>
+        <v>0.0567187547645229</v>
       </c>
       <c r="F24" s="21">
-        <v>0.04466876110564888</v>
+        <v>0.04582767345940343</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2452,19 +2452,19 @@
         <v>106</v>
       </c>
       <c r="B25" s="21">
-        <v>0.09393310648210551</v>
+        <v>0.10910471047537063</v>
       </c>
       <c r="C25" s="21">
-        <v>-0.06579539044035591</v>
+        <v>-0.051422243907954454</v>
       </c>
       <c r="D25" s="21">
-        <v>-0.2095510403635472</v>
+        <v>-0.19589666517629928</v>
       </c>
       <c r="E25" s="21">
-        <v>-0.3396158174638573</v>
+        <v>-0.3266114689579745</v>
       </c>
       <c r="F25" s="21">
-        <v>-0.45785638676297546</v>
+        <v>-0.445443114251158</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2472,19 +2472,19 @@
         <v>107</v>
       </c>
       <c r="B26" s="21">
-        <v>0.12057981523916945</v>
+        <v>0.12810132114761058</v>
       </c>
       <c r="C26" s="21">
-        <v>0.03845582838183949</v>
+        <v>0.04608182576932193</v>
       </c>
       <c r="D26" s="21">
-        <v>-0.04079581405598358</v>
+        <v>-0.033017220094952365</v>
       </c>
       <c r="E26" s="21">
-        <v>-0.11797669982171974</v>
+        <v>-0.10998774803393488</v>
       </c>
       <c r="F26" s="21">
-        <v>-0.19388908345421896</v>
+        <v>-0.1856177603886407</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,19 +2492,19 @@
         <v>108</v>
       </c>
       <c r="B27" s="21">
-        <v>0.1276889043143744</v>
+        <v>0.13262357512450512</v>
       </c>
       <c r="C27" s="21">
-        <v>0.07337219919853706</v>
+        <v>0.07845041833109456</v>
       </c>
       <c r="D27" s="21">
-        <v>0.020166241259089453</v>
+        <v>0.025423827479639994</v>
       </c>
       <c r="E27" s="21">
-        <v>-0.03242900355630119</v>
+        <v>-0.026948421097821716</v>
       </c>
       <c r="F27" s="21">
-        <v>-0.08493204787352922</v>
+        <v>-0.07917391661462109</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2512,19 +2512,19 @@
         <v>109</v>
       </c>
       <c r="B28" s="21">
-        <v>0.1300035602581548</v>
+        <v>0.13365674787741055</v>
       </c>
       <c r="C28" s="21">
-        <v>0.08973195985586083</v>
+        <v>0.09350158245052509</v>
       </c>
       <c r="D28" s="21">
-        <v>0.05018624686841496</v>
+        <v>0.0540977817607695</v>
       </c>
       <c r="E28" s="21">
-        <v>0.011019662274355496</v>
+        <v>0.01510360051660006</v>
       </c>
       <c r="F28" s="21">
-        <v>-0.028121628739957445</v>
+        <v>-0.023828043613982948</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2532,19 +2532,19 @@
         <v>110</v>
       </c>
       <c r="B29" s="21">
-        <v>0.13057795958295043</v>
+        <v>0.13347494885129463</v>
       </c>
       <c r="C29" s="21">
-        <v>0.09866834126858745</v>
+        <v>0.10165302822068639</v>
       </c>
       <c r="D29" s="21">
-        <v>0.06739054190722293</v>
+        <v>0.07048128522568808</v>
       </c>
       <c r="E29" s="21">
-        <v>0.036486780221911236</v>
+        <v>0.03970501618398531</v>
       </c>
       <c r="F29" s="21">
-        <v>0.0057017926618013436</v>
+        <v>0.00907297502739949</v>
       </c>
     </row>
   </sheetData>
